--- a/实验1_miniRV_数据通路与控制信号_V1.1.xlsx
+++ b/实验1_miniRV_数据通路与控制信号_V1.1.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Morro\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Code\CPUDesign\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B1ECC451-8239-440D-9670-25B2FB69677A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{342EC410-6BA5-4C85-91B3-39159C375629}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="数据通路表(含控制信号)" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1434" uniqueCount="187">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1434" uniqueCount="186">
   <si>
     <t>数据通路表-示例</t>
   </si>
@@ -201,9 +201,6 @@
 SEXT.ext
 MEXT.ext
 NPC.pc4</t>
-  </si>
-  <si>
-    <t>IN.inst[31:7]</t>
   </si>
   <si>
     <t>RF.rD2
@@ -551,12 +548,6 @@
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
-    <t>IN.inst[31:12]
-IN.inst[31:20]
-IN.inst[31|7|30:25|11:8]</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
     <t>RF.rD2
 SEXT.ext</t>
     <phoneticPr fontId="6" type="noConversion"/>
@@ -602,6 +593,10 @@
   </si>
   <si>
     <t>miniRV A+B：数据通路表</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>IN.inst[31:7]</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
 </sst>
@@ -972,18 +967,111 @@
     <xf numFmtId="49" fontId="2" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -994,99 +1082,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1323,50 +1318,50 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B2" s="25" t="s">
+      <c r="B2" s="37" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="26"/>
-      <c r="D2" s="26"/>
-      <c r="E2" s="26"/>
-      <c r="F2" s="26"/>
-      <c r="G2" s="26"/>
-      <c r="H2" s="26"/>
-      <c r="I2" s="26"/>
-      <c r="J2" s="26"/>
-      <c r="K2" s="26"/>
-      <c r="L2" s="26"/>
-      <c r="M2" s="26"/>
-      <c r="N2" s="26"/>
-      <c r="O2" s="26"/>
+      <c r="C2" s="59"/>
+      <c r="D2" s="59"/>
+      <c r="E2" s="59"/>
+      <c r="F2" s="59"/>
+      <c r="G2" s="59"/>
+      <c r="H2" s="59"/>
+      <c r="I2" s="59"/>
+      <c r="J2" s="59"/>
+      <c r="K2" s="59"/>
+      <c r="L2" s="59"/>
+      <c r="M2" s="59"/>
+      <c r="N2" s="59"/>
+      <c r="O2" s="59"/>
     </row>
     <row r="3" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B3" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="29" t="s">
+      <c r="C3" s="60" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="30"/>
-      <c r="E3" s="30"/>
-      <c r="F3" s="30"/>
-      <c r="G3" s="29" t="s">
+      <c r="D3" s="61"/>
+      <c r="E3" s="61"/>
+      <c r="F3" s="61"/>
+      <c r="G3" s="60" t="s">
         <v>3</v>
       </c>
-      <c r="H3" s="30"/>
-      <c r="I3" s="30"/>
-      <c r="J3" s="30"/>
-      <c r="K3" s="31"/>
-      <c r="L3" s="29" t="s">
+      <c r="H3" s="61"/>
+      <c r="I3" s="61"/>
+      <c r="J3" s="61"/>
+      <c r="K3" s="62"/>
+      <c r="L3" s="60" t="s">
         <v>4</v>
       </c>
-      <c r="M3" s="31"/>
-      <c r="N3" s="33" t="s">
+      <c r="M3" s="62"/>
+      <c r="N3" s="41" t="s">
         <v>5</v>
       </c>
-      <c r="O3" s="33"/>
-      <c r="P3" s="33"/>
-      <c r="Q3" s="33"/>
+      <c r="O3" s="41"/>
+      <c r="P3" s="41"/>
+      <c r="Q3" s="41"/>
     </row>
     <row r="4" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B4" s="8" t="s">
@@ -1375,32 +1370,32 @@
       <c r="C4" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="D4" s="27" t="s">
+      <c r="D4" s="57" t="s">
         <v>8</v>
       </c>
-      <c r="E4" s="32"/>
-      <c r="F4" s="28"/>
-      <c r="G4" s="27" t="s">
+      <c r="E4" s="63"/>
+      <c r="F4" s="58"/>
+      <c r="G4" s="57" t="s">
         <v>9</v>
       </c>
-      <c r="H4" s="32"/>
-      <c r="I4" s="32"/>
-      <c r="J4" s="28"/>
+      <c r="H4" s="63"/>
+      <c r="I4" s="63"/>
+      <c r="J4" s="58"/>
       <c r="K4" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="L4" s="27" t="s">
+      <c r="L4" s="57" t="s">
         <v>11</v>
       </c>
-      <c r="M4" s="28"/>
-      <c r="N4" s="27" t="s">
+      <c r="M4" s="58"/>
+      <c r="N4" s="57" t="s">
         <v>12</v>
       </c>
-      <c r="O4" s="28"/>
-      <c r="P4" s="27" t="s">
+      <c r="O4" s="58"/>
+      <c r="P4" s="57" t="s">
         <v>13</v>
       </c>
-      <c r="Q4" s="28"/>
+      <c r="Q4" s="58"/>
     </row>
     <row r="5" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B5" s="8" t="s">
@@ -1880,14 +1875,14 @@
       <c r="J14" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="K14" s="4" t="s">
-        <v>59</v>
+      <c r="K14" s="11" t="s">
+        <v>185</v>
       </c>
       <c r="L14" s="4" t="s">
         <v>38</v>
       </c>
       <c r="M14" s="5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="N14" s="4" t="s">
         <v>36</v>
@@ -1904,79 +1899,79 @@
     </row>
     <row r="15" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B15" s="9" t="s">
+        <v>60</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="D15" s="57" t="s">
         <v>61</v>
       </c>
-      <c r="C15" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="D15" s="27" t="s">
+      <c r="E15" s="63"/>
+      <c r="F15" s="58"/>
+      <c r="G15" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="H15" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="I15" s="57" t="s">
         <v>62</v>
       </c>
-      <c r="E15" s="32"/>
-      <c r="F15" s="28"/>
-      <c r="G15" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="H15" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="I15" s="27" t="s">
+      <c r="J15" s="58"/>
+      <c r="K15" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="J15" s="28"/>
-      <c r="K15" s="4" t="s">
+      <c r="L15" s="57" t="s">
         <v>64</v>
       </c>
-      <c r="L15" s="27" t="s">
+      <c r="M15" s="58"/>
+      <c r="N15" s="57" t="s">
         <v>65</v>
       </c>
-      <c r="M15" s="28"/>
-      <c r="N15" s="27" t="s">
-        <v>66</v>
-      </c>
-      <c r="O15" s="28"/>
-      <c r="P15" s="27" t="s">
-        <v>66</v>
-      </c>
-      <c r="Q15" s="28"/>
+      <c r="O15" s="58"/>
+      <c r="P15" s="57" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q15" s="58"/>
     </row>
     <row r="16" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B16" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="E16" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="F16" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="G16" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="H16" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="I16" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="J16" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="C16" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="D16" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="E16" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="F16" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="G16" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="H16" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="I16" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="J16" s="4" t="s">
+      <c r="K16" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="L16" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="M16" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="K16" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="L16" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="M16" s="4" t="s">
-        <v>69</v>
-      </c>
       <c r="N16" s="4" t="s">
         <v>33</v>
       </c>
@@ -1991,52 +1986,52 @@
       </c>
     </row>
     <row r="18" spans="2:17" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="B18" s="34" t="s">
-        <v>186</v>
-      </c>
-      <c r="C18" s="35"/>
-      <c r="D18" s="35"/>
-      <c r="E18" s="35"/>
-      <c r="F18" s="35"/>
-      <c r="G18" s="35"/>
-      <c r="H18" s="35"/>
-      <c r="I18" s="35"/>
-      <c r="J18" s="35"/>
-      <c r="K18" s="35"/>
-      <c r="L18" s="35"/>
-      <c r="M18" s="35"/>
-      <c r="N18" s="35"/>
-      <c r="O18" s="35"/>
-      <c r="P18" s="35"/>
-      <c r="Q18" s="36"/>
+      <c r="B18" s="42" t="s">
+        <v>184</v>
+      </c>
+      <c r="C18" s="43"/>
+      <c r="D18" s="43"/>
+      <c r="E18" s="43"/>
+      <c r="F18" s="43"/>
+      <c r="G18" s="43"/>
+      <c r="H18" s="43"/>
+      <c r="I18" s="43"/>
+      <c r="J18" s="43"/>
+      <c r="K18" s="43"/>
+      <c r="L18" s="43"/>
+      <c r="M18" s="43"/>
+      <c r="N18" s="43"/>
+      <c r="O18" s="43"/>
+      <c r="P18" s="43"/>
+      <c r="Q18" s="44"/>
     </row>
     <row r="19" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B19" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="C19" s="45" t="s">
+      <c r="C19" s="53" t="s">
         <v>2</v>
       </c>
-      <c r="D19" s="46"/>
-      <c r="E19" s="46"/>
-      <c r="F19" s="46"/>
-      <c r="G19" s="45" t="s">
+      <c r="D19" s="54"/>
+      <c r="E19" s="54"/>
+      <c r="F19" s="54"/>
+      <c r="G19" s="53" t="s">
         <v>3</v>
       </c>
-      <c r="H19" s="46"/>
-      <c r="I19" s="46"/>
-      <c r="J19" s="46"/>
-      <c r="K19" s="47"/>
-      <c r="L19" s="45" t="s">
+      <c r="H19" s="54"/>
+      <c r="I19" s="54"/>
+      <c r="J19" s="54"/>
+      <c r="K19" s="55"/>
+      <c r="L19" s="53" t="s">
         <v>4</v>
       </c>
-      <c r="M19" s="47"/>
-      <c r="N19" s="48" t="s">
+      <c r="M19" s="55"/>
+      <c r="N19" s="56" t="s">
         <v>5</v>
       </c>
-      <c r="O19" s="48"/>
-      <c r="P19" s="48"/>
-      <c r="Q19" s="48"/>
+      <c r="O19" s="56"/>
+      <c r="P19" s="56"/>
+      <c r="Q19" s="56"/>
     </row>
     <row r="20" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B20" s="6" t="s">
@@ -2045,32 +2040,32 @@
       <c r="C20" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D20" s="42" t="s">
+      <c r="D20" s="50" t="s">
         <v>8</v>
       </c>
-      <c r="E20" s="44"/>
-      <c r="F20" s="43"/>
-      <c r="G20" s="42" t="s">
+      <c r="E20" s="52"/>
+      <c r="F20" s="51"/>
+      <c r="G20" s="50" t="s">
         <v>9</v>
       </c>
-      <c r="H20" s="44"/>
-      <c r="I20" s="44"/>
-      <c r="J20" s="43"/>
+      <c r="H20" s="52"/>
+      <c r="I20" s="52"/>
+      <c r="J20" s="51"/>
       <c r="K20" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L20" s="42" t="s">
+      <c r="L20" s="50" t="s">
         <v>11</v>
       </c>
-      <c r="M20" s="43"/>
-      <c r="N20" s="42" t="s">
+      <c r="M20" s="51"/>
+      <c r="N20" s="50" t="s">
         <v>12</v>
       </c>
-      <c r="O20" s="43"/>
-      <c r="P20" s="42" t="s">
+      <c r="O20" s="51"/>
+      <c r="P20" s="50" t="s">
         <v>13</v>
       </c>
-      <c r="Q20" s="43"/>
+      <c r="Q20" s="51"/>
     </row>
     <row r="21" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B21" s="6" t="s">
@@ -2124,7 +2119,7 @@
     </row>
     <row r="22" spans="2:17" ht="23.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B22" s="12" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C22" s="3" t="s">
         <v>31</v>
@@ -2174,7 +2169,7 @@
     </row>
     <row r="23" spans="2:17" ht="23.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B23" s="12" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C23" s="3" t="s">
         <v>31</v>
@@ -2224,7 +2219,7 @@
     </row>
     <row r="24" spans="2:17" ht="23.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B24" s="12" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C24" s="3" t="s">
         <v>31</v>
@@ -2274,7 +2269,7 @@
     </row>
     <row r="25" spans="2:17" ht="23.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B25" s="12" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C25" s="3" t="s">
         <v>31</v>
@@ -2324,7 +2319,7 @@
     </row>
     <row r="26" spans="2:17" ht="23.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B26" s="12" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C26" s="3" t="s">
         <v>31</v>
@@ -2374,7 +2369,7 @@
     </row>
     <row r="27" spans="2:17" ht="23.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B27" s="12" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C27" s="3" t="s">
         <v>31</v>
@@ -2424,7 +2419,7 @@
     </row>
     <row r="28" spans="2:17" ht="23.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B28" s="12" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C28" s="3" t="s">
         <v>31</v>
@@ -2474,7 +2469,7 @@
     </row>
     <row r="29" spans="2:17" ht="23.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B29" s="12" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C29" s="3" t="s">
         <v>31</v>
@@ -2524,7 +2519,7 @@
     </row>
     <row r="30" spans="2:17" ht="23.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B30" s="12" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C30" s="3" t="s">
         <v>31</v>
@@ -2574,7 +2569,7 @@
     </row>
     <row r="31" spans="2:17" ht="23.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B31" s="12" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C31" s="3" t="s">
         <v>31</v>
@@ -2624,7 +2619,7 @@
     </row>
     <row r="32" spans="2:17" ht="23.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B32" s="12" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C32" s="3" t="s">
         <v>31</v>
@@ -2674,7 +2669,7 @@
     </row>
     <row r="33" spans="2:17" ht="23.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B33" s="12" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C33" s="3" t="s">
         <v>31</v>
@@ -2724,7 +2719,7 @@
     </row>
     <row r="34" spans="2:17" ht="23.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B34" s="12" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C34" s="3" t="s">
         <v>31</v>
@@ -2774,7 +2769,7 @@
     </row>
     <row r="35" spans="2:17" ht="23.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B35" s="12" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C35" s="3" t="s">
         <v>31</v>
@@ -2824,7 +2819,7 @@
     </row>
     <row r="36" spans="2:17" ht="23.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B36" s="12" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C36" s="3" t="s">
         <v>31</v>
@@ -2851,7 +2846,7 @@
         <v>33</v>
       </c>
       <c r="K36" s="21" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="L36" s="3" t="s">
         <v>38</v>
@@ -2874,7 +2869,7 @@
     </row>
     <row r="37" spans="2:17" ht="23.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B37" s="12" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C37" s="3" t="s">
         <v>31</v>
@@ -2924,7 +2919,7 @@
     </row>
     <row r="38" spans="2:17" ht="23.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B38" s="12" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C38" s="3" t="s">
         <v>31</v>
@@ -2974,7 +2969,7 @@
     </row>
     <row r="39" spans="2:17" ht="23.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B39" s="12" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C39" s="3" t="s">
         <v>31</v>
@@ -3024,7 +3019,7 @@
     </row>
     <row r="40" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B40" s="23" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C40" s="1" t="s">
         <v>31</v>
@@ -3074,7 +3069,7 @@
     </row>
     <row r="41" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B41" s="23" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C41" s="1" t="s">
         <v>31</v>
@@ -3124,7 +3119,7 @@
     </row>
     <row r="42" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B42" s="23" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C42" s="1" t="s">
         <v>31</v>
@@ -3151,7 +3146,7 @@
         <v>36</v>
       </c>
       <c r="K42" s="22" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="L42" s="1" t="s">
         <v>32</v>
@@ -3174,7 +3169,7 @@
     </row>
     <row r="43" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B43" s="23" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C43" s="1" t="s">
         <v>31</v>
@@ -3224,7 +3219,7 @@
     </row>
     <row r="44" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B44" s="23" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C44" s="1" t="s">
         <v>31</v>
@@ -3251,7 +3246,7 @@
         <v>36</v>
       </c>
       <c r="K44" s="22" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="L44" s="1" t="s">
         <v>38</v>
@@ -3274,7 +3269,7 @@
     </row>
     <row r="45" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B45" s="23" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C45" s="1" t="s">
         <v>31</v>
@@ -3324,7 +3319,7 @@
     </row>
     <row r="46" spans="2:17" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B46" s="23" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C46" s="1" t="s">
         <v>31</v>
@@ -3374,7 +3369,7 @@
     </row>
     <row r="47" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B47" s="23" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C47" s="1" t="s">
         <v>31</v>
@@ -3424,7 +3419,7 @@
     </row>
     <row r="48" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B48" s="23" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C48" s="1" t="s">
         <v>31</v>
@@ -3474,7 +3469,7 @@
     </row>
     <row r="49" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B49" s="23" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C49" s="1" t="s">
         <v>31</v>
@@ -3524,7 +3519,7 @@
     </row>
     <row r="50" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B50" s="23" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C50" s="1" t="s">
         <v>31</v>
@@ -3574,7 +3569,7 @@
     </row>
     <row r="51" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B51" s="23" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C51" s="1" t="s">
         <v>31</v>
@@ -3624,7 +3619,7 @@
     </row>
     <row r="52" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B52" s="23" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C52" s="1" t="s">
         <v>31</v>
@@ -3674,7 +3669,7 @@
     </row>
     <row r="53" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B53" s="23" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C53" s="1" t="s">
         <v>31</v>
@@ -3724,7 +3719,7 @@
     </row>
     <row r="54" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B54" s="23" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C54" s="1" t="s">
         <v>31</v>
@@ -3751,7 +3746,7 @@
         <v>33</v>
       </c>
       <c r="K54" s="1" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="L54" s="1" t="s">
         <v>38</v>
@@ -3774,7 +3769,7 @@
     </row>
     <row r="55" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B55" s="23" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C55" s="1" t="s">
         <v>31</v>
@@ -3801,7 +3796,7 @@
         <v>33</v>
       </c>
       <c r="K55" s="1" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="L55" s="1" t="s">
         <v>38</v>
@@ -3824,7 +3819,7 @@
     </row>
     <row r="56" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B56" s="23" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C56" s="1" t="s">
         <v>31</v>
@@ -3851,7 +3846,7 @@
         <v>33</v>
       </c>
       <c r="K56" s="1" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="L56" s="1" t="s">
         <v>38</v>
@@ -3874,7 +3869,7 @@
     </row>
     <row r="57" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B57" s="23" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C57" s="1" t="s">
         <v>31</v>
@@ -3948,22 +3943,22 @@
         <v>35</v>
       </c>
       <c r="J58" s="20" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="K58" s="20" t="s">
-        <v>172</v>
+        <v>185</v>
       </c>
       <c r="L58" s="3" t="s">
         <v>38</v>
       </c>
       <c r="M58" s="20" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="N58" s="3" t="s">
         <v>36</v>
       </c>
       <c r="O58" s="21" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="P58" s="3" t="s">
         <v>46</v>
@@ -3974,80 +3969,80 @@
     </row>
     <row r="59" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B59" s="13" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C59" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="D59" s="37" t="s">
-        <v>148</v>
-      </c>
-      <c r="E59" s="38"/>
-      <c r="F59" s="39"/>
+      <c r="D59" s="45" t="s">
+        <v>147</v>
+      </c>
+      <c r="E59" s="46"/>
+      <c r="F59" s="47"/>
       <c r="G59" s="3" t="s">
         <v>33</v>
       </c>
       <c r="H59" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="I59" s="40" t="s">
+      <c r="I59" s="48" t="s">
+        <v>62</v>
+      </c>
+      <c r="J59" s="49"/>
+      <c r="K59" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="J59" s="41"/>
-      <c r="K59" s="3" t="s">
+      <c r="L59" s="48" t="s">
         <v>64</v>
       </c>
-      <c r="L59" s="40" t="s">
+      <c r="M59" s="49"/>
+      <c r="N59" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="M59" s="41"/>
-      <c r="N59" s="3" t="s">
-        <v>66</v>
-      </c>
       <c r="O59" s="3" t="s">
-        <v>125</v>
-      </c>
-      <c r="P59" s="40" t="s">
-        <v>66</v>
-      </c>
-      <c r="Q59" s="41"/>
+        <v>124</v>
+      </c>
+      <c r="P59" s="48" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q59" s="49"/>
     </row>
     <row r="60" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B60" s="13" t="s">
+        <v>66</v>
+      </c>
+      <c r="C60" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D60" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="E60" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F60" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="G60" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="H60" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="I60" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="J60" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="C60" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="D60" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="E60" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="F60" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="G60" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="H60" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="I60" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="J60" s="3" t="s">
+      <c r="K60" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="L60" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="M60" s="3" t="s">
         <v>68</v>
-      </c>
-      <c r="K60" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="L60" s="3" t="s">
-        <v>126</v>
-      </c>
-      <c r="M60" s="3" t="s">
-        <v>69</v>
       </c>
       <c r="N60" s="3" t="s">
         <v>33</v>
@@ -4064,6 +4059,21 @@
     </row>
   </sheetData>
   <mergeCells count="29">
+    <mergeCell ref="B2:O2"/>
+    <mergeCell ref="I15:J15"/>
+    <mergeCell ref="L15:M15"/>
+    <mergeCell ref="C3:F3"/>
+    <mergeCell ref="G3:K3"/>
+    <mergeCell ref="L3:M3"/>
+    <mergeCell ref="D4:F4"/>
+    <mergeCell ref="G4:J4"/>
+    <mergeCell ref="L4:M4"/>
+    <mergeCell ref="D15:F15"/>
+    <mergeCell ref="P4:Q4"/>
+    <mergeCell ref="P15:Q15"/>
+    <mergeCell ref="N3:Q3"/>
+    <mergeCell ref="N15:O15"/>
+    <mergeCell ref="N4:O4"/>
     <mergeCell ref="B18:Q18"/>
     <mergeCell ref="D59:F59"/>
     <mergeCell ref="I59:J59"/>
@@ -4078,21 +4088,6 @@
     <mergeCell ref="L20:M20"/>
     <mergeCell ref="N19:Q19"/>
     <mergeCell ref="P20:Q20"/>
-    <mergeCell ref="P4:Q4"/>
-    <mergeCell ref="P15:Q15"/>
-    <mergeCell ref="N3:Q3"/>
-    <mergeCell ref="N15:O15"/>
-    <mergeCell ref="N4:O4"/>
-    <mergeCell ref="B2:O2"/>
-    <mergeCell ref="I15:J15"/>
-    <mergeCell ref="L15:M15"/>
-    <mergeCell ref="C3:F3"/>
-    <mergeCell ref="G3:K3"/>
-    <mergeCell ref="L3:M3"/>
-    <mergeCell ref="D4:F4"/>
-    <mergeCell ref="G4:J4"/>
-    <mergeCell ref="L4:M4"/>
-    <mergeCell ref="D15:F15"/>
   </mergeCells>
   <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4120,16 +4115,16 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B2" s="25" t="s">
-        <v>70</v>
-      </c>
-      <c r="C2" s="25"/>
-      <c r="D2" s="25"/>
-      <c r="E2" s="25"/>
-      <c r="F2" s="25"/>
-      <c r="G2" s="25"/>
-      <c r="H2" s="25"/>
-      <c r="I2" s="25"/>
+      <c r="B2" s="37" t="s">
+        <v>69</v>
+      </c>
+      <c r="C2" s="37"/>
+      <c r="D2" s="37"/>
+      <c r="E2" s="37"/>
+      <c r="F2" s="37"/>
+      <c r="G2" s="37"/>
+      <c r="H2" s="37"/>
+      <c r="I2" s="37"/>
       <c r="J2" s="10"/>
       <c r="K2" s="10"/>
       <c r="L2" s="10"/>
@@ -4138,56 +4133,56 @@
       <c r="O2" s="10"/>
     </row>
     <row r="3" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B3" s="49" t="s">
+      <c r="B3" s="38" t="s">
+        <v>70</v>
+      </c>
+      <c r="C3" s="39" t="s">
         <v>71</v>
       </c>
-      <c r="C3" s="50" t="s">
+      <c r="D3" s="39" t="s">
         <v>72</v>
       </c>
-      <c r="D3" s="50" t="s">
+      <c r="E3" s="39" t="s">
         <v>73</v>
       </c>
-      <c r="E3" s="50" t="s">
+      <c r="F3" s="41" t="s">
         <v>74</v>
       </c>
-      <c r="F3" s="33" t="s">
-        <v>75</v>
-      </c>
-      <c r="G3" s="33"/>
-      <c r="H3" s="33"/>
-      <c r="I3" s="33"/>
-      <c r="J3" s="33"/>
-      <c r="K3" s="33"/>
-      <c r="L3" s="33"/>
+      <c r="G3" s="41"/>
+      <c r="H3" s="41"/>
+      <c r="I3" s="41"/>
+      <c r="J3" s="41"/>
+      <c r="K3" s="41"/>
+      <c r="L3" s="41"/>
       <c r="M3"/>
       <c r="N3"/>
       <c r="O3"/>
     </row>
     <row r="4" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B4" s="49"/>
-      <c r="C4" s="51"/>
-      <c r="D4" s="51"/>
-      <c r="E4" s="51"/>
+      <c r="B4" s="38"/>
+      <c r="C4" s="40"/>
+      <c r="D4" s="40"/>
+      <c r="E4" s="40"/>
       <c r="F4" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="G4" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="G4" s="7" t="s">
+      <c r="H4" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="I4" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="H4" s="7" t="s">
+      <c r="J4" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="K4" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="I4" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="J4" s="7" t="s">
+      <c r="L4" s="7" t="s">
         <v>65</v>
-      </c>
-      <c r="K4" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="L4" s="7" t="s">
-        <v>66</v>
       </c>
       <c r="M4"/>
       <c r="N4"/>
@@ -4198,34 +4193,34 @@
         <v>30</v>
       </c>
       <c r="C5" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="D5" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="D5" s="7" t="s">
+      <c r="E5" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="F5" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="E5" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="F5" s="7" t="s">
+      <c r="G5" s="7" t="s">
         <v>78</v>
       </c>
-      <c r="G5" s="7" t="s">
+      <c r="H5" s="7" t="s">
         <v>79</v>
       </c>
-      <c r="H5" s="7" t="s">
+      <c r="I5" s="7" t="s">
         <v>80</v>
       </c>
-      <c r="I5" s="7" t="s">
+      <c r="J5" s="7" t="s">
         <v>81</v>
       </c>
-      <c r="J5" s="7" t="s">
+      <c r="K5" s="7" t="s">
         <v>82</v>
       </c>
-      <c r="K5" s="7" t="s">
-        <v>83</v>
-      </c>
       <c r="L5" s="7" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="M5"/>
       <c r="N5"/>
@@ -4236,34 +4231,34 @@
         <v>40</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D6" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="E6" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="F6" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="G6" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="H6" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="I6" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="J6" s="7" t="s">
         <v>85</v>
       </c>
-      <c r="E6" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="F6" s="7" t="s">
-        <v>78</v>
-      </c>
-      <c r="G6" s="7" t="s">
-        <v>79</v>
-      </c>
-      <c r="H6" s="7" t="s">
-        <v>80</v>
-      </c>
-      <c r="I6" s="7" t="s">
-        <v>81</v>
-      </c>
-      <c r="J6" s="7" t="s">
-        <v>86</v>
-      </c>
       <c r="K6" s="7" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="L6" s="7" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="M6"/>
       <c r="N6"/>
@@ -4274,34 +4269,34 @@
         <v>41</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D7" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="E7" s="7" t="s">
         <v>87</v>
       </c>
-      <c r="E7" s="7" t="s">
+      <c r="F7" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="G7" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="H7" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="I7" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="J7" s="7" t="s">
         <v>88</v>
       </c>
-      <c r="F7" s="7" t="s">
-        <v>78</v>
-      </c>
-      <c r="G7" s="7" t="s">
-        <v>79</v>
-      </c>
-      <c r="H7" s="7" t="s">
-        <v>80</v>
-      </c>
-      <c r="I7" s="7" t="s">
-        <v>81</v>
-      </c>
-      <c r="J7" s="7" t="s">
-        <v>89</v>
-      </c>
       <c r="K7" s="7" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="L7" s="7" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="M7"/>
       <c r="N7"/>
@@ -4312,26 +4307,26 @@
         <v>42</v>
       </c>
       <c r="C8" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="D8" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="E8" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="F8" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="G8" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="H8" s="7" t="s">
         <v>90</v>
       </c>
-      <c r="D8" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="E8" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="F8" s="7" t="s">
-        <v>78</v>
-      </c>
-      <c r="G8" s="7" t="s">
-        <v>79</v>
-      </c>
-      <c r="H8" s="7" t="s">
+      <c r="I8" s="7" t="s">
         <v>91</v>
       </c>
-      <c r="I8" s="7" t="s">
-        <v>92</v>
-      </c>
       <c r="J8" s="7" t="s">
         <v>33</v>
       </c>
@@ -4339,7 +4334,7 @@
         <v>33</v>
       </c>
       <c r="L8" s="7" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="M8"/>
       <c r="N8"/>
@@ -4350,34 +4345,34 @@
         <v>44</v>
       </c>
       <c r="C9" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="D9" s="7" t="s">
         <v>93</v>
       </c>
-      <c r="D9" s="7" t="s">
+      <c r="E9" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="F9" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="G9" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="H9" s="7" t="s">
         <v>94</v>
       </c>
-      <c r="E9" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="F9" s="7" t="s">
-        <v>78</v>
-      </c>
-      <c r="G9" s="7" t="s">
-        <v>79</v>
-      </c>
-      <c r="H9" s="7" t="s">
+      <c r="I9" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="J9" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="K9" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="L9" s="7" t="s">
         <v>95</v>
-      </c>
-      <c r="I9" s="7" t="s">
-        <v>81</v>
-      </c>
-      <c r="J9" s="7" t="s">
-        <v>82</v>
-      </c>
-      <c r="K9" s="7" t="s">
-        <v>83</v>
-      </c>
-      <c r="L9" s="7" t="s">
-        <v>96</v>
       </c>
       <c r="M9"/>
       <c r="N9"/>
@@ -4388,16 +4383,16 @@
         <v>48</v>
       </c>
       <c r="C10" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="D10" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="E10" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="F10" s="7" t="s">
         <v>97</v>
-      </c>
-      <c r="D10" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="E10" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="F10" s="7" t="s">
-        <v>98</v>
       </c>
       <c r="G10" s="4">
         <v>0</v>
@@ -4406,16 +4401,16 @@
         <v>33</v>
       </c>
       <c r="I10" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="J10" s="7" t="s">
         <v>99</v>
       </c>
-      <c r="J10" s="7" t="s">
+      <c r="K10" s="7" t="s">
         <v>100</v>
       </c>
-      <c r="K10" s="7" t="s">
-        <v>101</v>
-      </c>
       <c r="L10" s="7" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="M10"/>
       <c r="N10"/>
@@ -4426,16 +4421,16 @@
         <v>53</v>
       </c>
       <c r="C11" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="D11" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="E11" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="F11" s="7" t="s">
         <v>97</v>
-      </c>
-      <c r="D11" s="7" t="s">
-        <v>87</v>
-      </c>
-      <c r="E11" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="F11" s="7" t="s">
-        <v>98</v>
       </c>
       <c r="G11" s="4">
         <v>0</v>
@@ -4444,16 +4439,16 @@
         <v>33</v>
       </c>
       <c r="I11" s="7" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="J11" s="7" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="K11" s="7" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="L11" s="7" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="M11"/>
       <c r="N11"/>
@@ -4464,26 +4459,26 @@
         <v>54</v>
       </c>
       <c r="C12" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="D12" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="E12" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="F12" s="7" t="s">
         <v>103</v>
-      </c>
-      <c r="D12" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="E12" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="F12" s="7" t="s">
-        <v>104</v>
       </c>
       <c r="G12" s="4">
         <v>1</v>
       </c>
       <c r="H12" s="7" t="s">
+        <v>104</v>
+      </c>
+      <c r="I12" s="7" t="s">
         <v>105</v>
       </c>
-      <c r="I12" s="7" t="s">
-        <v>106</v>
-      </c>
       <c r="J12" s="7" t="s">
         <v>33</v>
       </c>
@@ -4491,1614 +4486,1614 @@
         <v>33</v>
       </c>
       <c r="L12" s="7" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="M12"/>
       <c r="N12"/>
       <c r="O12"/>
     </row>
     <row r="14" spans="2:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="B14" s="61" t="s">
-        <v>185</v>
-      </c>
-      <c r="C14" s="62"/>
-      <c r="D14" s="62"/>
-      <c r="E14" s="62"/>
-      <c r="F14" s="62"/>
-      <c r="G14" s="62"/>
-      <c r="H14" s="62"/>
-      <c r="I14" s="62"/>
-      <c r="J14" s="62"/>
-      <c r="K14" s="62"/>
-      <c r="L14" s="62"/>
-      <c r="M14" s="62"/>
-      <c r="N14" s="62"/>
-      <c r="O14" s="62"/>
-      <c r="P14" s="63"/>
+      <c r="B14" s="32" t="s">
+        <v>183</v>
+      </c>
+      <c r="C14" s="33"/>
+      <c r="D14" s="33"/>
+      <c r="E14" s="33"/>
+      <c r="F14" s="33"/>
+      <c r="G14" s="33"/>
+      <c r="H14" s="33"/>
+      <c r="I14" s="33"/>
+      <c r="J14" s="33"/>
+      <c r="K14" s="33"/>
+      <c r="L14" s="33"/>
+      <c r="M14" s="33"/>
+      <c r="N14" s="33"/>
+      <c r="O14" s="33"/>
+      <c r="P14" s="34"/>
     </row>
     <row r="15" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B15" s="52" t="s">
+      <c r="B15" s="28" t="s">
+        <v>70</v>
+      </c>
+      <c r="C15" s="30" t="s">
         <v>71</v>
       </c>
-      <c r="C15" s="54" t="s">
+      <c r="D15" s="30" t="s">
         <v>72</v>
       </c>
-      <c r="D15" s="54" t="s">
+      <c r="E15" s="30" t="s">
         <v>73</v>
       </c>
-      <c r="E15" s="54" t="s">
+      <c r="F15" s="35" t="s">
         <v>74</v>
       </c>
-      <c r="F15" s="59" t="s">
-        <v>75</v>
-      </c>
-      <c r="G15" s="60"/>
-      <c r="H15" s="60"/>
-      <c r="I15" s="60"/>
-      <c r="J15" s="60"/>
-      <c r="K15" s="60"/>
-      <c r="L15" s="60"/>
-      <c r="M15" s="60"/>
-      <c r="N15" s="60"/>
-      <c r="O15" s="60"/>
-      <c r="P15" s="60"/>
+      <c r="G15" s="36"/>
+      <c r="H15" s="36"/>
+      <c r="I15" s="36"/>
+      <c r="J15" s="36"/>
+      <c r="K15" s="36"/>
+      <c r="L15" s="36"/>
+      <c r="M15" s="36"/>
+      <c r="N15" s="36"/>
+      <c r="O15" s="36"/>
+      <c r="P15" s="36"/>
     </row>
     <row r="16" spans="2:16" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="B16" s="53" t="s">
+      <c r="B16" s="29" t="s">
+        <v>70</v>
+      </c>
+      <c r="C16" s="31" t="s">
         <v>71</v>
       </c>
-      <c r="C16" s="55" t="s">
+      <c r="D16" s="31" t="s">
         <v>72</v>
       </c>
-      <c r="D16" s="55" t="s">
+      <c r="E16" s="31" t="s">
         <v>73</v>
       </c>
-      <c r="E16" s="55" t="s">
-        <v>74</v>
-      </c>
       <c r="F16" s="14" t="s">
+        <v>61</v>
+      </c>
+      <c r="G16" s="14" t="s">
         <v>62</v>
       </c>
-      <c r="G16" s="14" t="s">
+      <c r="H16" s="14" t="s">
+        <v>67</v>
+      </c>
+      <c r="I16" s="14" t="s">
         <v>63</v>
       </c>
-      <c r="H16" s="14" t="s">
+      <c r="J16" s="14" t="s">
+        <v>64</v>
+      </c>
+      <c r="K16" s="14" t="s">
+        <v>125</v>
+      </c>
+      <c r="L16" s="14" t="s">
         <v>68</v>
       </c>
-      <c r="I16" s="14" t="s">
-        <v>64</v>
-      </c>
-      <c r="J16" s="14" t="s">
+      <c r="M16" s="14" t="s">
         <v>65</v>
       </c>
-      <c r="K16" s="14" t="s">
-        <v>126</v>
-      </c>
-      <c r="L16" s="14" t="s">
-        <v>69</v>
-      </c>
-      <c r="M16" s="14" t="s">
-        <v>66</v>
-      </c>
       <c r="N16" s="14" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="O16"/>
     </row>
     <row r="17" spans="2:15" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B17" s="15" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C17" s="16" t="s">
+        <v>126</v>
+      </c>
+      <c r="D17" s="17" t="s">
+        <v>76</v>
+      </c>
+      <c r="E17" s="16" t="s">
         <v>127</v>
       </c>
-      <c r="D17" s="17" t="s">
+      <c r="F17" s="18" t="s">
         <v>77</v>
       </c>
-      <c r="E17" s="16" t="s">
+      <c r="G17" s="18" t="s">
+        <v>78</v>
+      </c>
+      <c r="H17" s="18" t="s">
+        <v>79</v>
+      </c>
+      <c r="I17" s="18" t="s">
+        <v>33</v>
+      </c>
+      <c r="J17" s="18" t="s">
         <v>128</v>
       </c>
-      <c r="F17" s="18" t="s">
-        <v>78</v>
-      </c>
-      <c r="G17" s="18" t="s">
-        <v>79</v>
-      </c>
-      <c r="H17" s="18" t="s">
-        <v>80</v>
-      </c>
-      <c r="I17" s="18" t="s">
-        <v>33</v>
-      </c>
-      <c r="J17" s="18" t="s">
+      <c r="K17" s="18" t="s">
         <v>129</v>
       </c>
-      <c r="K17" s="18" t="s">
-        <v>130</v>
-      </c>
       <c r="L17" s="18" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="M17" s="18" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="N17" s="18" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="O17"/>
     </row>
     <row r="18" spans="2:15" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B18" s="15" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C18" s="16" t="s">
+        <v>126</v>
+      </c>
+      <c r="D18" s="17" t="s">
+        <v>86</v>
+      </c>
+      <c r="E18" s="16" t="s">
         <v>127</v>
       </c>
-      <c r="D18" s="17" t="s">
-        <v>87</v>
-      </c>
-      <c r="E18" s="16" t="s">
-        <v>128</v>
-      </c>
       <c r="F18" s="18" t="s">
+        <v>77</v>
+      </c>
+      <c r="G18" s="18" t="s">
         <v>78</v>
       </c>
-      <c r="G18" s="18" t="s">
+      <c r="H18" s="18" t="s">
         <v>79</v>
       </c>
-      <c r="H18" s="18" t="s">
-        <v>80</v>
-      </c>
       <c r="I18" s="18" t="s">
         <v>33</v>
       </c>
       <c r="J18" s="18" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="K18" s="18" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="L18" s="18" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="M18" s="18" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="N18" s="18" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="O18"/>
     </row>
     <row r="19" spans="2:15" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B19" s="15" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C19" s="16" t="s">
+        <v>126</v>
+      </c>
+      <c r="D19" s="17" t="s">
+        <v>131</v>
+      </c>
+      <c r="E19" s="16" t="s">
         <v>127</v>
       </c>
-      <c r="D19" s="17" t="s">
+      <c r="F19" s="18" t="s">
+        <v>77</v>
+      </c>
+      <c r="G19" s="18" t="s">
+        <v>78</v>
+      </c>
+      <c r="H19" s="18" t="s">
+        <v>79</v>
+      </c>
+      <c r="I19" s="18" t="s">
+        <v>33</v>
+      </c>
+      <c r="J19" s="18" t="s">
         <v>132</v>
       </c>
-      <c r="E19" s="16" t="s">
-        <v>128</v>
-      </c>
-      <c r="F19" s="18" t="s">
-        <v>78</v>
-      </c>
-      <c r="G19" s="18" t="s">
-        <v>79</v>
-      </c>
-      <c r="H19" s="18" t="s">
-        <v>80</v>
-      </c>
-      <c r="I19" s="18" t="s">
-        <v>33</v>
-      </c>
-      <c r="J19" s="18" t="s">
-        <v>133</v>
-      </c>
       <c r="K19" s="18" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="L19" s="18" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="M19" s="18" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="N19" s="18" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="O19"/>
     </row>
     <row r="20" spans="2:15" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B20" s="15" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C20" s="16" t="s">
+        <v>126</v>
+      </c>
+      <c r="D20" s="17" t="s">
+        <v>133</v>
+      </c>
+      <c r="E20" s="16" t="s">
         <v>127</v>
       </c>
-      <c r="D20" s="17" t="s">
+      <c r="F20" s="18" t="s">
+        <v>77</v>
+      </c>
+      <c r="G20" s="18" t="s">
+        <v>78</v>
+      </c>
+      <c r="H20" s="18" t="s">
+        <v>79</v>
+      </c>
+      <c r="I20" s="18" t="s">
+        <v>33</v>
+      </c>
+      <c r="J20" s="18" t="s">
         <v>134</v>
       </c>
-      <c r="E20" s="16" t="s">
-        <v>128</v>
-      </c>
-      <c r="F20" s="18" t="s">
-        <v>78</v>
-      </c>
-      <c r="G20" s="18" t="s">
-        <v>79</v>
-      </c>
-      <c r="H20" s="18" t="s">
-        <v>80</v>
-      </c>
-      <c r="I20" s="18" t="s">
-        <v>33</v>
-      </c>
-      <c r="J20" s="18" t="s">
-        <v>135</v>
-      </c>
       <c r="K20" s="18" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="L20" s="18" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="M20" s="18" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="N20" s="18" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="O20"/>
     </row>
     <row r="21" spans="2:15" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B21" s="15" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C21" s="16" t="s">
+        <v>126</v>
+      </c>
+      <c r="D21" s="17" t="s">
+        <v>135</v>
+      </c>
+      <c r="E21" s="16" t="s">
         <v>127</v>
       </c>
-      <c r="D21" s="17" t="s">
+      <c r="F21" s="18" t="s">
+        <v>77</v>
+      </c>
+      <c r="G21" s="18" t="s">
+        <v>78</v>
+      </c>
+      <c r="H21" s="18" t="s">
+        <v>79</v>
+      </c>
+      <c r="I21" s="18" t="s">
+        <v>33</v>
+      </c>
+      <c r="J21" s="18" t="s">
         <v>136</v>
       </c>
-      <c r="E21" s="16" t="s">
-        <v>128</v>
-      </c>
-      <c r="F21" s="18" t="s">
-        <v>78</v>
-      </c>
-      <c r="G21" s="18" t="s">
-        <v>79</v>
-      </c>
-      <c r="H21" s="18" t="s">
-        <v>80</v>
-      </c>
-      <c r="I21" s="18" t="s">
-        <v>33</v>
-      </c>
-      <c r="J21" s="18" t="s">
-        <v>137</v>
-      </c>
       <c r="K21" s="18" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="L21" s="18" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="M21" s="18" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="N21" s="18" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="O21"/>
     </row>
     <row r="22" spans="2:15" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B22" s="15" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C22" s="16" t="s">
+        <v>126</v>
+      </c>
+      <c r="D22" s="17" t="s">
+        <v>84</v>
+      </c>
+      <c r="E22" s="16" t="s">
         <v>127</v>
       </c>
-      <c r="D22" s="17" t="s">
-        <v>85</v>
-      </c>
-      <c r="E22" s="16" t="s">
-        <v>128</v>
-      </c>
       <c r="F22" s="18" t="s">
+        <v>77</v>
+      </c>
+      <c r="G22" s="18" t="s">
         <v>78</v>
       </c>
-      <c r="G22" s="18" t="s">
+      <c r="H22" s="18" t="s">
         <v>79</v>
       </c>
-      <c r="H22" s="18" t="s">
-        <v>80</v>
-      </c>
       <c r="I22" s="18" t="s">
         <v>33</v>
       </c>
       <c r="J22" s="18" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="K22" s="18" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="L22" s="18" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="M22" s="18" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="N22" s="18" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="O22"/>
     </row>
     <row r="23" spans="2:15" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B23" s="15" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C23" s="16" t="s">
+        <v>126</v>
+      </c>
+      <c r="D23" s="17" t="s">
+        <v>138</v>
+      </c>
+      <c r="E23" s="16" t="s">
         <v>127</v>
       </c>
-      <c r="D23" s="17" t="s">
+      <c r="F23" s="18" t="s">
+        <v>77</v>
+      </c>
+      <c r="G23" s="18" t="s">
+        <v>78</v>
+      </c>
+      <c r="H23" s="18" t="s">
+        <v>79</v>
+      </c>
+      <c r="I23" s="18" t="s">
+        <v>33</v>
+      </c>
+      <c r="J23" s="18" t="s">
         <v>139</v>
       </c>
-      <c r="E23" s="16" t="s">
-        <v>128</v>
-      </c>
-      <c r="F23" s="18" t="s">
-        <v>78</v>
-      </c>
-      <c r="G23" s="18" t="s">
-        <v>79</v>
-      </c>
-      <c r="H23" s="18" t="s">
-        <v>80</v>
-      </c>
-      <c r="I23" s="18" t="s">
-        <v>33</v>
-      </c>
-      <c r="J23" s="18" t="s">
-        <v>140</v>
-      </c>
       <c r="K23" s="18" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="L23" s="18" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="M23" s="18" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="N23" s="18" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="O23"/>
     </row>
     <row r="24" spans="2:15" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B24" s="15" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C24" s="16" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D24" s="17" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E24" s="16" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F24" s="18" t="s">
+        <v>77</v>
+      </c>
+      <c r="G24" s="18" t="s">
         <v>78</v>
       </c>
-      <c r="G24" s="18" t="s">
+      <c r="H24" s="18" t="s">
         <v>79</v>
       </c>
-      <c r="H24" s="18" t="s">
-        <v>80</v>
-      </c>
       <c r="I24" s="18" t="s">
         <v>33</v>
       </c>
       <c r="J24" s="18" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="K24" s="18" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="L24" s="18" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="M24" s="18" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="N24" s="18" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="O24"/>
     </row>
     <row r="25" spans="2:15" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B25" s="15" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C25" s="16" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D25" s="17" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E25" s="16" t="s">
         <v>33</v>
       </c>
       <c r="F25" s="18" t="s">
+        <v>77</v>
+      </c>
+      <c r="G25" s="18" t="s">
         <v>78</v>
       </c>
-      <c r="G25" s="18" t="s">
+      <c r="H25" s="18" t="s">
         <v>79</v>
       </c>
-      <c r="H25" s="18" t="s">
+      <c r="I25" s="18" t="s">
         <v>80</v>
       </c>
-      <c r="I25" s="18" t="s">
-        <v>81</v>
-      </c>
       <c r="J25" s="18" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="K25" s="18" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="L25" s="18" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="M25" s="18" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="N25" s="18" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="O25"/>
     </row>
     <row r="26" spans="2:15" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B26" s="15" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C26" s="16" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D26" s="17" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E26" s="16" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F26" s="18" t="s">
+        <v>77</v>
+      </c>
+      <c r="G26" s="18" t="s">
         <v>78</v>
       </c>
-      <c r="G26" s="18" t="s">
+      <c r="H26" s="18" t="s">
         <v>79</v>
       </c>
-      <c r="H26" s="18" t="s">
-        <v>80</v>
-      </c>
       <c r="I26" s="18" t="s">
         <v>33</v>
       </c>
       <c r="J26" s="18" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="K26" s="18" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="L26" s="18" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="M26" s="18" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="N26" s="18" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="O26"/>
     </row>
     <row r="27" spans="2:15" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B27" s="15" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C27" s="16" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D27" s="17" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E27" s="16" t="s">
         <v>33</v>
       </c>
       <c r="F27" s="18" t="s">
+        <v>77</v>
+      </c>
+      <c r="G27" s="18" t="s">
         <v>78</v>
       </c>
-      <c r="G27" s="18" t="s">
+      <c r="H27" s="18" t="s">
         <v>79</v>
       </c>
-      <c r="H27" s="18" t="s">
+      <c r="I27" s="18" t="s">
         <v>80</v>
       </c>
-      <c r="I27" s="18" t="s">
-        <v>81</v>
-      </c>
       <c r="J27" s="18" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="K27" s="18" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="L27" s="18" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="M27" s="18" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="N27" s="18" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="O27"/>
     </row>
     <row r="28" spans="2:15" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B28" s="15" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C28" s="16" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D28" s="17" t="s">
+        <v>84</v>
+      </c>
+      <c r="E28" s="16" t="s">
+        <v>87</v>
+      </c>
+      <c r="F28" s="18" t="s">
+        <v>77</v>
+      </c>
+      <c r="G28" s="18" t="s">
+        <v>78</v>
+      </c>
+      <c r="H28" s="18" t="s">
+        <v>79</v>
+      </c>
+      <c r="I28" s="18" t="s">
+        <v>33</v>
+      </c>
+      <c r="J28" s="18" t="s">
         <v>85</v>
       </c>
-      <c r="E28" s="16" t="s">
-        <v>88</v>
-      </c>
-      <c r="F28" s="18" t="s">
-        <v>78</v>
-      </c>
-      <c r="G28" s="18" t="s">
-        <v>79</v>
-      </c>
-      <c r="H28" s="18" t="s">
-        <v>80</v>
-      </c>
-      <c r="I28" s="18" t="s">
-        <v>33</v>
-      </c>
-      <c r="J28" s="18" t="s">
-        <v>86</v>
-      </c>
       <c r="K28" s="18" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="L28" s="18" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="M28" s="18" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="N28" s="18" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="O28"/>
     </row>
     <row r="29" spans="2:15" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B29" s="15" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C29" s="16" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D29" s="17" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="E29" s="16" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F29" s="18" t="s">
+        <v>77</v>
+      </c>
+      <c r="G29" s="18" t="s">
         <v>78</v>
       </c>
-      <c r="G29" s="18" t="s">
+      <c r="H29" s="18" t="s">
         <v>79</v>
       </c>
-      <c r="H29" s="18" t="s">
-        <v>80</v>
-      </c>
       <c r="I29" s="18" t="s">
         <v>33</v>
       </c>
       <c r="J29" s="18" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="K29" s="18" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="L29" s="18" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="M29" s="18" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="N29" s="18" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="O29"/>
     </row>
     <row r="30" spans="2:15" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B30" s="15" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C30" s="16" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D30" s="17" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="E30" s="16" t="s">
         <v>33</v>
       </c>
       <c r="F30" s="18" t="s">
+        <v>77</v>
+      </c>
+      <c r="G30" s="18" t="s">
         <v>78</v>
       </c>
-      <c r="G30" s="18" t="s">
+      <c r="H30" s="18" t="s">
         <v>79</v>
       </c>
-      <c r="H30" s="18" t="s">
+      <c r="I30" s="18" t="s">
         <v>80</v>
       </c>
-      <c r="I30" s="18" t="s">
-        <v>81</v>
-      </c>
       <c r="J30" s="18" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="K30" s="18" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="L30" s="18" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="M30" s="18" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="N30" s="18" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="O30"/>
     </row>
     <row r="31" spans="2:15" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B31" s="15" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C31" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="D31" s="17" t="s">
+        <v>133</v>
+      </c>
+      <c r="E31" s="16" t="s">
+        <v>33</v>
+      </c>
+      <c r="F31" s="18" t="s">
         <v>97</v>
       </c>
-      <c r="D31" s="17" t="s">
-        <v>134</v>
-      </c>
-      <c r="E31" s="16" t="s">
-        <v>33</v>
-      </c>
-      <c r="F31" s="18" t="s">
+      <c r="G31" s="18" t="s">
+        <v>83</v>
+      </c>
+      <c r="H31" s="18" t="s">
+        <v>33</v>
+      </c>
+      <c r="I31" s="18" t="s">
         <v>98</v>
       </c>
-      <c r="G31" s="18" t="s">
-        <v>84</v>
-      </c>
-      <c r="H31" s="18" t="s">
-        <v>33</v>
-      </c>
-      <c r="I31" s="18" t="s">
-        <v>99</v>
-      </c>
       <c r="J31" s="18" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="K31" s="18" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="L31" s="18" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="M31" s="18" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="N31" s="18" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="O31"/>
     </row>
     <row r="32" spans="2:15" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B32" s="15" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C32" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="D32" s="17" t="s">
+        <v>135</v>
+      </c>
+      <c r="E32" s="16" t="s">
+        <v>33</v>
+      </c>
+      <c r="F32" s="18" t="s">
         <v>97</v>
       </c>
-      <c r="D32" s="17" t="s">
-        <v>136</v>
-      </c>
-      <c r="E32" s="16" t="s">
-        <v>33</v>
-      </c>
-      <c r="F32" s="18" t="s">
+      <c r="G32" s="18" t="s">
+        <v>83</v>
+      </c>
+      <c r="H32" s="18" t="s">
+        <v>33</v>
+      </c>
+      <c r="I32" s="18" t="s">
         <v>98</v>
       </c>
-      <c r="G32" s="18" t="s">
-        <v>84</v>
-      </c>
-      <c r="H32" s="18" t="s">
-        <v>33</v>
-      </c>
-      <c r="I32" s="18" t="s">
-        <v>99</v>
-      </c>
       <c r="J32" s="18" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="K32" s="18" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="L32" s="18" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="M32" s="18" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="N32" s="18" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="O32"/>
     </row>
     <row r="33" spans="2:15" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B33" s="15" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C33" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="D33" s="17" t="s">
+        <v>84</v>
+      </c>
+      <c r="E33" s="16" t="s">
+        <v>33</v>
+      </c>
+      <c r="F33" s="18" t="s">
         <v>97</v>
       </c>
-      <c r="D33" s="17" t="s">
-        <v>85</v>
-      </c>
-      <c r="E33" s="16" t="s">
-        <v>33</v>
-      </c>
-      <c r="F33" s="18" t="s">
+      <c r="G33" s="18" t="s">
+        <v>83</v>
+      </c>
+      <c r="H33" s="18" t="s">
+        <v>33</v>
+      </c>
+      <c r="I33" s="18" t="s">
         <v>98</v>
       </c>
-      <c r="G33" s="18" t="s">
-        <v>84</v>
-      </c>
-      <c r="H33" s="18" t="s">
-        <v>33</v>
-      </c>
-      <c r="I33" s="18" t="s">
-        <v>99</v>
-      </c>
       <c r="J33" s="18" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="K33" s="18" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="L33" s="18" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="M33" s="18" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="N33" s="18" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="O33"/>
     </row>
     <row r="34" spans="2:15" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B34" s="15" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C34" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="D34" s="17" t="s">
+        <v>138</v>
+      </c>
+      <c r="E34" s="16" t="s">
+        <v>33</v>
+      </c>
+      <c r="F34" s="18" t="s">
         <v>97</v>
       </c>
-      <c r="D34" s="17" t="s">
-        <v>139</v>
-      </c>
-      <c r="E34" s="16" t="s">
-        <v>33</v>
-      </c>
-      <c r="F34" s="18" t="s">
+      <c r="G34" s="18" t="s">
+        <v>83</v>
+      </c>
+      <c r="H34" s="18" t="s">
+        <v>33</v>
+      </c>
+      <c r="I34" s="18" t="s">
         <v>98</v>
       </c>
-      <c r="G34" s="18" t="s">
-        <v>84</v>
-      </c>
-      <c r="H34" s="18" t="s">
-        <v>33</v>
-      </c>
-      <c r="I34" s="18" t="s">
-        <v>99</v>
-      </c>
       <c r="J34" s="18" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="K34" s="18" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="L34" s="18" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="M34" s="18" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="N34" s="18" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="O34"/>
     </row>
     <row r="35" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B35" s="58" t="s">
+      <c r="B35" s="27" t="s">
+        <v>148</v>
+      </c>
+      <c r="C35" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="D35" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="E35" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="F35" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="G35" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="H35" s="25" t="s">
+        <v>79</v>
+      </c>
+      <c r="I35" s="25" t="s">
+        <v>33</v>
+      </c>
+      <c r="J35" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="K35" s="18" t="s">
+        <v>129</v>
+      </c>
+      <c r="L35" s="25" t="s">
+        <v>100</v>
+      </c>
+      <c r="M35" s="25" t="s">
+        <v>83</v>
+      </c>
+      <c r="N35" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="O35"/>
+    </row>
+    <row r="36" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B36" s="27" t="s">
         <v>149</v>
       </c>
-      <c r="C35" s="3" t="s">
-        <v>127</v>
-      </c>
-      <c r="D35" s="3" t="s">
+      <c r="C36" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="D36" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="E36" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="F36" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="E35" s="3" t="s">
+      <c r="G36" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="H36" s="25" t="s">
+        <v>79</v>
+      </c>
+      <c r="I36" s="25" t="s">
+        <v>33</v>
+      </c>
+      <c r="J36" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="K36" s="18" t="s">
+        <v>129</v>
+      </c>
+      <c r="L36" s="25" t="s">
+        <v>100</v>
+      </c>
+      <c r="M36" s="25" t="s">
+        <v>83</v>
+      </c>
+      <c r="N36" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="O36"/>
+    </row>
+    <row r="37" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B37" s="27" t="s">
+        <v>150</v>
+      </c>
+      <c r="C37" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="D37" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="E37" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F37" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="G37" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="H37" s="25" t="s">
+        <v>79</v>
+      </c>
+      <c r="I37" s="25" t="s">
+        <v>91</v>
+      </c>
+      <c r="J37" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="K37" s="26" t="s">
+        <v>182</v>
+      </c>
+      <c r="L37" s="25" t="s">
+        <v>82</v>
+      </c>
+      <c r="M37" s="25" t="s">
+        <v>83</v>
+      </c>
+      <c r="N37" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="O37"/>
+    </row>
+    <row r="38" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B38" s="27" t="s">
+        <v>151</v>
+      </c>
+      <c r="C38" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="D38" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="E38" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="F38" s="25" t="s">
+        <v>77</v>
+      </c>
+      <c r="G38" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="H38" s="25" t="s">
+        <v>79</v>
+      </c>
+      <c r="I38" s="25" t="s">
+        <v>33</v>
+      </c>
+      <c r="J38" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="K38" s="18" t="s">
+        <v>129</v>
+      </c>
+      <c r="L38" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="M38" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="N38" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="O38"/>
+    </row>
+    <row r="39" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B39" s="27" t="s">
+        <v>152</v>
+      </c>
+      <c r="C39" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="D39" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="E39" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F39" s="25" t="s">
+        <v>77</v>
+      </c>
+      <c r="G39" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="H39" s="25" t="s">
+        <v>79</v>
+      </c>
+      <c r="I39" s="25" t="s">
+        <v>80</v>
+      </c>
+      <c r="J39" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="K39" s="18" t="s">
+        <v>129</v>
+      </c>
+      <c r="L39" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="M39" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="N39" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="O39"/>
+    </row>
+    <row r="40" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B40" s="27" t="s">
+        <v>153</v>
+      </c>
+      <c r="C40" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="D40" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="E40" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="F40" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="G40" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="H40" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="I40" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="J40" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="F35" s="3" t="s">
+      <c r="K40" s="18" t="s">
+        <v>129</v>
+      </c>
+      <c r="L40" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="M40" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="N40" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="O40"/>
+    </row>
+    <row r="41" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B41" s="27" t="s">
+        <v>154</v>
+      </c>
+      <c r="C41" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="D41" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="E41" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="F41" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="G41" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="G35" s="3" t="s">
+      <c r="H41" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="H35" s="56" t="s">
+      <c r="I41" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="J41" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="K41" s="18" t="s">
+        <v>129</v>
+      </c>
+      <c r="L41" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="M41" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="N41" s="3" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="42" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B42" s="27" t="s">
+        <v>155</v>
+      </c>
+      <c r="C42" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="D42" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="E42" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F42" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="G42" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="H42" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="I42" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="I35" s="56" t="s">
-        <v>33</v>
-      </c>
-      <c r="J35" s="3" t="s">
+      <c r="J42" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="K42" s="18" t="s">
+        <v>129</v>
+      </c>
+      <c r="L42" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="K35" s="18" t="s">
-        <v>130</v>
-      </c>
-      <c r="L35" s="56" t="s">
-        <v>101</v>
-      </c>
-      <c r="M35" s="56" t="s">
-        <v>84</v>
-      </c>
-      <c r="N35" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="O35"/>
-    </row>
-    <row r="36" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B36" s="58" t="s">
-        <v>150</v>
-      </c>
-      <c r="C36" s="3" t="s">
-        <v>127</v>
-      </c>
-      <c r="D36" s="3" t="s">
+      <c r="M42" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="N42" s="3" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="43" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B43" s="27" t="s">
+        <v>156</v>
+      </c>
+      <c r="C43" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="D43" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="E43" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="F43" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="E36" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="F36" s="3" t="s">
+      <c r="G43" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="G36" s="3" t="s">
+      <c r="H43" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="H36" s="56" t="s">
+      <c r="I43" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="J43" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="K43" s="18" t="s">
+        <v>129</v>
+      </c>
+      <c r="L43" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="M43" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="N43" s="3" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="44" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B44" s="27" t="s">
+        <v>157</v>
+      </c>
+      <c r="C44" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="D44" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="I44" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="I36" s="56" t="s">
-        <v>33</v>
-      </c>
-      <c r="J36" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="K36" s="18" t="s">
-        <v>130</v>
-      </c>
-      <c r="L36" s="56" t="s">
-        <v>101</v>
-      </c>
-      <c r="M36" s="56" t="s">
-        <v>84</v>
-      </c>
-      <c r="N36" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="O36"/>
-    </row>
-    <row r="37" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B37" s="58" t="s">
-        <v>151</v>
-      </c>
-      <c r="C37" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="D37" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="E37" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="F37" s="3" t="s">
+      <c r="J44" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="K44" s="18" t="s">
+        <v>129</v>
+      </c>
+      <c r="L44" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="M44" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="N44" s="3" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="45" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B45" s="27" t="s">
+        <v>158</v>
+      </c>
+      <c r="C45" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="D45" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F45" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="G45" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="G37" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="H37" s="56" t="s">
+      <c r="H45" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="I45" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="I37" s="56" t="s">
+      <c r="J45" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="K45" s="18" t="s">
+        <v>129</v>
+      </c>
+      <c r="L45" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="M45" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="N45" s="3" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="46" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B46" s="27" t="s">
+        <v>159</v>
+      </c>
+      <c r="C46" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="J37" s="3" t="s">
+      <c r="D46" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="E46" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F46" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="G46" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="H46" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="I46" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="J46" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="K46" s="18" t="s">
+        <v>129</v>
+      </c>
+      <c r="L46" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="K37" s="57" t="s">
-        <v>184</v>
-      </c>
-      <c r="L37" s="56" t="s">
-        <v>83</v>
-      </c>
-      <c r="M37" s="56" t="s">
-        <v>84</v>
-      </c>
-      <c r="N37" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="O37"/>
-    </row>
-    <row r="38" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B38" s="58" t="s">
-        <v>152</v>
-      </c>
-      <c r="C38" s="3" t="s">
-        <v>127</v>
-      </c>
-      <c r="D38" s="3" t="s">
-        <v>134</v>
-      </c>
-      <c r="E38" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="F38" s="56" t="s">
+      <c r="M46" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="G38" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="H38" s="56" t="s">
+      <c r="N46" s="3" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="47" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B47" s="27" t="s">
+        <v>160</v>
+      </c>
+      <c r="C47" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="D47" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="I47" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="I38" s="56" t="s">
-        <v>33</v>
-      </c>
-      <c r="J38" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="K38" s="18" t="s">
-        <v>130</v>
-      </c>
-      <c r="L38" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="M38" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="N38" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="O38"/>
-    </row>
-    <row r="39" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B39" s="58" t="s">
-        <v>153</v>
-      </c>
-      <c r="C39" s="3" t="s">
+      <c r="J47" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="K47" s="18" t="s">
+        <v>129</v>
+      </c>
+      <c r="L47" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="M47" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="N47" s="3" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="48" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B48" s="27" t="s">
+        <v>161</v>
+      </c>
+      <c r="C48" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="D48" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="E48" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F48" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="G48" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="H48" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="I48" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="J48" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="K48" s="18" t="s">
+        <v>129</v>
+      </c>
+      <c r="L48" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="M48" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="N48" s="3" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="49" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B49" s="27" t="s">
+        <v>162</v>
+      </c>
+      <c r="C49" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="D49" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="E49" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F49" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="G49" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="H49" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="I49" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="J49" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="K49" s="18" t="s">
+        <v>129</v>
+      </c>
+      <c r="L49" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="M49" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="N49" s="3" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="50" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B50" s="27" t="s">
+        <v>164</v>
+      </c>
+      <c r="C50" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="D50" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="D39" s="3" t="s">
-        <v>134</v>
-      </c>
-      <c r="E39" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="F39" s="56" t="s">
+      <c r="E50" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F50" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="G50" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="H50" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="I50" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="J50" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="K50" s="18" t="s">
+        <v>129</v>
+      </c>
+      <c r="L50" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="M50" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="N50" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="G39" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="H39" s="56" t="s">
+    </row>
+    <row r="51" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B51" s="27" t="s">
+        <v>165</v>
+      </c>
+      <c r="C51" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="D51" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="E51" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F51" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="G51" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="H51" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="I51" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="J51" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="K51" s="18" t="s">
+        <v>129</v>
+      </c>
+      <c r="L51" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="M51" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="N51" s="3" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="52" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B52" s="27" t="s">
+        <v>166</v>
+      </c>
+      <c r="C52" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="D52" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="E52" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F52" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="G52" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="H52" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="I52" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="I39" s="56" t="s">
+      <c r="J52" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="J39" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="K39" s="18" t="s">
-        <v>130</v>
-      </c>
-      <c r="L39" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="M39" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="N39" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="O39"/>
-    </row>
-    <row r="40" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B40" s="58" t="s">
-        <v>154</v>
-      </c>
-      <c r="C40" s="3" t="s">
-        <v>127</v>
-      </c>
-      <c r="D40" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="E40" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="F40" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="G40" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="H40" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="I40" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="J40" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="K40" s="18" t="s">
-        <v>130</v>
-      </c>
-      <c r="L40" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="M40" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="N40" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="O40"/>
-    </row>
-    <row r="41" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B41" s="58" t="s">
-        <v>155</v>
-      </c>
-      <c r="C41" s="3" t="s">
-        <v>127</v>
-      </c>
-      <c r="D41" s="3" t="s">
-        <v>136</v>
-      </c>
-      <c r="E41" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="F41" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="G41" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="H41" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="I41" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="J41" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="K41" s="18" t="s">
-        <v>130</v>
-      </c>
-      <c r="L41" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="M41" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="N41" s="3" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="42" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B42" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="C42" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="D42" s="3" t="s">
-        <v>136</v>
-      </c>
-      <c r="E42" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="F42" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="G42" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="H42" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="I42" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="J42" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="K42" s="18" t="s">
-        <v>130</v>
-      </c>
-      <c r="L42" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="M42" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="N42" s="3" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="43" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B43" s="58" t="s">
-        <v>157</v>
-      </c>
-      <c r="C43" s="3" t="s">
-        <v>127</v>
-      </c>
-      <c r="D43" s="3" t="s">
-        <v>136</v>
-      </c>
-      <c r="E43" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="F43" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="G43" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="H43" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="I43" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="J43" s="3" t="s">
-        <v>180</v>
-      </c>
-      <c r="K43" s="18" t="s">
-        <v>130</v>
-      </c>
-      <c r="L43" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="M43" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="N43" s="3" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="44" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B44" s="58" t="s">
-        <v>158</v>
-      </c>
-      <c r="C44" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="D44" s="3" t="s">
-        <v>136</v>
-      </c>
-      <c r="E44" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="F44" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="G44" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="H44" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="I44" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="J44" s="3" t="s">
-        <v>180</v>
-      </c>
-      <c r="K44" s="18" t="s">
-        <v>130</v>
-      </c>
-      <c r="L44" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="M44" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="N44" s="3" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="45" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B45" s="58" t="s">
-        <v>159</v>
-      </c>
-      <c r="C45" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="D45" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="E45" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="F45" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="G45" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="H45" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="I45" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="J45" s="3" t="s">
+      <c r="K52" s="18" t="s">
+        <v>129</v>
+      </c>
+      <c r="L52" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="K45" s="18" t="s">
-        <v>130</v>
-      </c>
-      <c r="L45" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="M45" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="N45" s="3" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="46" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B46" s="58" t="s">
-        <v>160</v>
-      </c>
-      <c r="C46" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="D46" s="3" t="s">
-        <v>134</v>
-      </c>
-      <c r="E46" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="F46" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="G46" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="H46" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="I46" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="J46" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="K46" s="18" t="s">
-        <v>130</v>
-      </c>
-      <c r="L46" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="M46" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="N46" s="3" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="47" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B47" s="58" t="s">
-        <v>161</v>
-      </c>
-      <c r="C47" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="D47" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="E47" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="F47" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="G47" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="H47" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="I47" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="J47" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="K47" s="18" t="s">
-        <v>130</v>
-      </c>
-      <c r="L47" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="M47" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="N47" s="3" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="48" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B48" s="58" t="s">
-        <v>162</v>
-      </c>
-      <c r="C48" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="D48" s="3" t="s">
-        <v>136</v>
-      </c>
-      <c r="E48" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="F48" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="G48" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="H48" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="I48" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="J48" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="K48" s="18" t="s">
-        <v>130</v>
-      </c>
-      <c r="L48" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="M48" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="N48" s="3" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="49" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B49" s="58" t="s">
-        <v>163</v>
-      </c>
-      <c r="C49" s="3" t="s">
-        <v>181</v>
-      </c>
-      <c r="D49" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="E49" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="F49" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="G49" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="H49" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="I49" s="3" t="s">
-        <v>182</v>
-      </c>
-      <c r="J49" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="K49" s="18" t="s">
-        <v>130</v>
-      </c>
-      <c r="L49" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="M49" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="N49" s="3" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="50" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B50" s="58" t="s">
-        <v>165</v>
-      </c>
-      <c r="C50" s="3" t="s">
-        <v>181</v>
-      </c>
-      <c r="D50" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="E50" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="F50" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="G50" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="H50" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="I50" s="3" t="s">
-        <v>182</v>
-      </c>
-      <c r="J50" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="K50" s="18" t="s">
-        <v>130</v>
-      </c>
-      <c r="L50" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="M50" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="N50" s="3" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="51" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B51" s="58" t="s">
-        <v>166</v>
-      </c>
-      <c r="C51" s="3" t="s">
-        <v>181</v>
-      </c>
-      <c r="D51" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="E51" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="F51" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="G51" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="H51" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="I51" s="3" t="s">
-        <v>182</v>
-      </c>
-      <c r="J51" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="K51" s="18" t="s">
-        <v>130</v>
-      </c>
-      <c r="L51" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="M51" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="N51" s="3" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="52" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B52" s="58" t="s">
-        <v>167</v>
-      </c>
-      <c r="C52" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="D52" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="E52" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="F52" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="G52" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="H52" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="I52" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="J52" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="K52" s="18" t="s">
-        <v>130</v>
-      </c>
-      <c r="L52" s="3" t="s">
-        <v>83</v>
-      </c>
       <c r="M52" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="N52" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="B2:I2"/>
+    <mergeCell ref="B3:B4"/>
+    <mergeCell ref="C3:C4"/>
+    <mergeCell ref="D3:D4"/>
+    <mergeCell ref="E3:E4"/>
+    <mergeCell ref="F3:L3"/>
     <mergeCell ref="B15:B16"/>
     <mergeCell ref="E15:E16"/>
     <mergeCell ref="C15:C16"/>
     <mergeCell ref="D15:D16"/>
     <mergeCell ref="B14:P14"/>
     <mergeCell ref="F15:P15"/>
-    <mergeCell ref="B2:I2"/>
-    <mergeCell ref="B3:B4"/>
-    <mergeCell ref="C3:C4"/>
-    <mergeCell ref="D3:D4"/>
-    <mergeCell ref="E3:E4"/>
-    <mergeCell ref="F3:L3"/>
   </mergeCells>
   <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
